--- a/data/trans_camb/IP16B98-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16B98-Clase-trans_camb.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-48,82; 76,95</t>
+          <t>-47,35; 80,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,03; 46,52</t>
+          <t>-25,5; 47,08</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-63,37; —</t>
+          <t>-58,66; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-35,18; 86,97</t>
+          <t>-26,32; 88,99</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,14</t>
+          <t>0,0; 42,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-34,54; 31,61</t>
+          <t>-37,8; 33,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 25,87</t>
+          <t>-15,33; 25,49</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,32</t>
+          <t>0,0; 77,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-39,53; 47,45</t>
+          <t>-40,73; 52,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 37,43</t>
+          <t>-16,47; 35,67</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 22,01</t>
+          <t>-2,85; 19,91</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 15,42</t>
+          <t>-11,74; 14,9</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 12,65</t>
+          <t>-5,05; 12,94</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 28,87</t>
+          <t>-2,86; 25,75</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 18,77</t>
+          <t>-12,63; 18,4</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 15,47</t>
+          <t>-5,31; 15,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B98-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16B98-Clase-trans_camb.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-47,35; 80,77</t>
+          <t>-48,82; 76,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 47,08</t>
+          <t>-25,75; 46,32</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-58,66; —</t>
+          <t>-65,16; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 88,99</t>
+          <t>-26,78; 83,96</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,5</t>
+          <t>0,0; 52,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-37,8; 33,47</t>
+          <t>-38,37; 30,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,33; 25,49</t>
+          <t>-14,24; 26,29</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,16</t>
+          <t>0,0; 113,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-40,73; 52,91</t>
+          <t>-42,69; 46,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 35,67</t>
+          <t>-15,22; 37,26</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 19,91</t>
+          <t>-2,72; 22,07</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 14,9</t>
+          <t>-13,21; 16,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 12,94</t>
+          <t>-5,93; 13,34</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 25,75</t>
+          <t>-2,72; 29,45</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 18,4</t>
+          <t>-13,87; 20,99</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 15,26</t>
+          <t>-6,08; 15,59</t>
         </is>
       </c>
     </row>
